--- a/tests/results/eval-log.xlsx
+++ b/tests/results/eval-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Reranked</t>
+  </si>
+  <si>
     <t>2026-08-12T11:54:46.293Z</t>
   </si>
   <si>
@@ -71,6 +74,18 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>2026-08-13T04:22:36.694Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T04-22-36-692Z.json</t>
+  </si>
+  <si>
+    <t>Voyage rerank-2.5 over top-20 candidates</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -451,13 +466,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="14" width="20" customWidth="1"/>
+    <col min="1" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,11 +514,14 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -539,15 +557,15 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>60</v>
@@ -583,10 +601,57 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>0.967</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0.983</v>
+      </c>
+      <c r="I4">
+        <v>0.988</v>
+      </c>
+      <c r="J4">
+        <v>0.923</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/tests/results/eval-log.xlsx
+++ b/tests/results/eval-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -58,6 +58,15 @@
     <t>Reranked</t>
   </si>
   <si>
+    <t>Multi-chunk Coverage</t>
+  </si>
+  <si>
+    <t>Unanswerable Suppression Rate</t>
+  </si>
+  <si>
+    <t>Avg Chunk Count</t>
+  </si>
+  <si>
     <t>2026-08-12T11:54:46.293Z</t>
   </si>
   <si>
@@ -86,6 +95,24 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>2026-08-13T04:54:16.581Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T04-54-16-580Z.json</t>
+  </si>
+  <si>
+    <t>baseline on extended golden set (71 q), before dynamic-k</t>
+  </si>
+  <si>
+    <t>2026-08-13T05:00:22.349Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T05-00-22-348Z.json</t>
+  </si>
+  <si>
+    <t>dynamic-k, threshold=0.65, maxK=8</t>
   </si>
 </sst>
 </file>
@@ -466,13 +493,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="15" width="20" customWidth="1"/>
+    <col min="1" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,11 +544,20 @@
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -557,15 +593,15 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>60</v>
@@ -601,15 +637,15 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>60</v>
@@ -645,13 +681,125 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>65</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>0.969</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0.985</v>
+      </c>
+      <c r="I5">
+        <v>0.984</v>
+      </c>
+      <c r="J5">
+        <v>0.923</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>0.969</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0.985</v>
+      </c>
+      <c r="I6">
+        <v>0.984</v>
+      </c>
+      <c r="J6">
+        <v>0.923</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6">
+        <v>0.4</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1.662</v>
       </c>
     </row>
   </sheetData>

--- a/tests/results/eval-log.xlsx
+++ b/tests/results/eval-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>Date</t>
   </si>
@@ -67,6 +67,21 @@
     <t>Avg Chunk Count</t>
   </si>
   <si>
+    <t>Answer Quality Pass Rate</t>
+  </si>
+  <si>
+    <t>Conversation Condensation Accuracy</t>
+  </si>
+  <si>
+    <t>Conversation Retrieval Recall</t>
+  </si>
+  <si>
+    <t>Decomposition Coverage (Triggered)</t>
+  </si>
+  <si>
+    <t>Decomposition Coverage (All Docs)</t>
+  </si>
+  <si>
     <t>2026-08-12T11:54:46.293Z</t>
   </si>
   <si>
@@ -113,6 +128,36 @@
   </si>
   <si>
     <t>dynamic-k, threshold=0.65, maxK=8</t>
+  </si>
+  <si>
+    <t>2026-08-13T05:09:30.479Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T05-09-30-478Z.json</t>
+  </si>
+  <si>
+    <t>dynamic-k, threshold=0.60, maxK=8</t>
+  </si>
+  <si>
+    <t>2026-08-13T08:48:03.378Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T08-48-03-371Z.json</t>
+  </si>
+  <si>
+    <t>baseline single-turn, phase 1</t>
+  </si>
+  <si>
+    <t>2026-08-13T09:09:51.844Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T09-09-51-839Z.json</t>
+  </si>
+  <si>
+    <t>phase3 conversations test</t>
+  </si>
+  <si>
+    <t>3/5</t>
   </si>
 </sst>
 </file>
@@ -493,13 +538,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="18" width="20" customWidth="1"/>
+    <col min="1" max="23" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,11 +598,26 @@
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>60</v>
@@ -593,15 +653,15 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>60</v>
@@ -637,15 +697,15 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>60</v>
@@ -681,18 +741,18 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="O4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>65</v>
@@ -728,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -748,7 +808,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>65</v>
@@ -784,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" t="s">
         <v>32</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" t="s">
-        <v>27</v>
       </c>
       <c r="P6">
         <v>0.4</v>
@@ -800,6 +860,192 @@
       </c>
       <c r="R6">
         <v>1.662</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7">
+        <v>65</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>0.969</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0.985</v>
+      </c>
+      <c r="I7">
+        <v>0.984</v>
+      </c>
+      <c r="J7">
+        <v>0.923</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7">
+        <v>0.8</v>
+      </c>
+      <c r="Q7">
+        <v>0.833</v>
+      </c>
+      <c r="R7">
+        <v>1.944</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8">
+        <v>65</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>0.969</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0.985</v>
+      </c>
+      <c r="I8">
+        <v>0.984</v>
+      </c>
+      <c r="J8">
+        <v>0.923</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8">
+        <v>0.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.833</v>
+      </c>
+      <c r="R8">
+        <v>1.944</v>
+      </c>
+      <c r="S8">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9">
+        <v>65</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>0.862</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0.923</v>
+      </c>
+      <c r="I9">
+        <v>0.94</v>
+      </c>
+      <c r="J9">
+        <v>0.692</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>8</v>
+      </c>
+      <c r="S9" t="s">
+        <v>28</v>
+      </c>
+      <c r="T9">
+        <v>0.6</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9" t="s">
+        <v>48</v>
+      </c>
+      <c r="W9" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/tests/results/eval-log.xlsx
+++ b/tests/results/eval-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -158,6 +158,18 @@
   </si>
   <si>
     <t>3/5</t>
+  </si>
+  <si>
+    <t>2026-08-13T09:29:11.426Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T09-29-11-423Z.json</t>
+  </si>
+  <si>
+    <t>fixed decomposition-coverage harness bug, re-check q062/q064</t>
+  </si>
+  <si>
+    <t>5/5</t>
   </si>
 </sst>
 </file>
@@ -538,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="23" width="20" customWidth="1"/>
@@ -1048,6 +1060,77 @@
         <v>48</v>
       </c>
     </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10">
+        <v>65</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>0.969</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0.985</v>
+      </c>
+      <c r="I10">
+        <v>0.984</v>
+      </c>
+      <c r="J10">
+        <v>0.923</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10">
+        <v>0.8</v>
+      </c>
+      <c r="Q10">
+        <v>0.833</v>
+      </c>
+      <c r="R10">
+        <v>1.944</v>
+      </c>
+      <c r="S10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10">
+        <v>0.533</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10" t="s">
+        <v>48</v>
+      </c>
+      <c r="W10" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/tests/results/eval-log.xlsx
+++ b/tests/results/eval-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -170,6 +170,69 @@
   </si>
   <si>
     <t>5/5</t>
+  </si>
+  <si>
+    <t>2026-08-13T09:51:01.597Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T09-51-01-595Z.json</t>
+  </si>
+  <si>
+    <t>current-state snapshot, post query-planner (phases 0-4)</t>
+  </si>
+  <si>
+    <t>2026-08-13T10:13:34.869Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T10-13-34-867Z.json</t>
+  </si>
+  <si>
+    <t>lexical categories baseline (vector-only)</t>
+  </si>
+  <si>
+    <t>2026-08-13T10:15:06.109Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T10-15-06-107Z.json</t>
+  </si>
+  <si>
+    <t>lexical categories baseline (reranked)</t>
+  </si>
+  <si>
+    <t>2026-08-13T10:34:59.123Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T10-34-59-120Z.json</t>
+  </si>
+  <si>
+    <t>hybrid dense+sparse (vector-only pass)</t>
+  </si>
+  <si>
+    <t>2026-08-13T10:36:21.805Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T10-36-21-799Z.json</t>
+  </si>
+  <si>
+    <t>hybrid dense+sparse (reranked pass)</t>
+  </si>
+  <si>
+    <t>2026-08-13T10:49:00.731Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T10-49-00-728Z.json</t>
+  </si>
+  <si>
+    <t>hybrid v2: OR-ified sparse query + phrase extraction (vector-only pass)</t>
+  </si>
+  <si>
+    <t>2026-08-13T10:52:33.573Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T10-52-33-570Z.json</t>
+  </si>
+  <si>
+    <t>hybrid v2: OR-ified sparse query + phrase extraction (reranked pass)</t>
   </si>
 </sst>
 </file>
@@ -550,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="23" width="20" customWidth="1"/>
@@ -1131,6 +1194,503 @@
         <v>52</v>
       </c>
     </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11">
+        <v>65</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>0.969</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0.985</v>
+      </c>
+      <c r="I11">
+        <v>0.984</v>
+      </c>
+      <c r="J11">
+        <v>0.923</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11">
+        <v>0.8</v>
+      </c>
+      <c r="Q11">
+        <v>0.833</v>
+      </c>
+      <c r="R11">
+        <v>1.944</v>
+      </c>
+      <c r="S11">
+        <v>0.972</v>
+      </c>
+      <c r="T11">
+        <v>0.6</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11" t="s">
+        <v>48</v>
+      </c>
+      <c r="W11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>89</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>0.865</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0.925</v>
+      </c>
+      <c r="I12">
+        <v>0.943</v>
+      </c>
+      <c r="J12">
+        <v>0.692</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" t="s">
+        <v>58</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>8</v>
+      </c>
+      <c r="S12" t="s">
+        <v>28</v>
+      </c>
+      <c r="T12" t="s">
+        <v>28</v>
+      </c>
+      <c r="U12" t="s">
+        <v>28</v>
+      </c>
+      <c r="V12" t="s">
+        <v>28</v>
+      </c>
+      <c r="W12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13">
+        <v>89</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>0.978</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0.989</v>
+      </c>
+      <c r="I13">
+        <v>0.989</v>
+      </c>
+      <c r="J13">
+        <v>0.923</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13">
+        <v>0.8</v>
+      </c>
+      <c r="Q13">
+        <v>0.833</v>
+      </c>
+      <c r="R13">
+        <v>1.811</v>
+      </c>
+      <c r="S13" t="s">
+        <v>28</v>
+      </c>
+      <c r="T13" t="s">
+        <v>28</v>
+      </c>
+      <c r="U13" t="s">
+        <v>28</v>
+      </c>
+      <c r="V13" t="s">
+        <v>28</v>
+      </c>
+      <c r="W13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>89</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>0.865</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0.925</v>
+      </c>
+      <c r="I14">
+        <v>0.943</v>
+      </c>
+      <c r="J14">
+        <v>0.692</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>8</v>
+      </c>
+      <c r="S14" t="s">
+        <v>28</v>
+      </c>
+      <c r="T14" t="s">
+        <v>28</v>
+      </c>
+      <c r="U14" t="s">
+        <v>28</v>
+      </c>
+      <c r="V14" t="s">
+        <v>28</v>
+      </c>
+      <c r="W14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15">
+        <v>89</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>0.978</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0.989</v>
+      </c>
+      <c r="I15">
+        <v>0.989</v>
+      </c>
+      <c r="J15">
+        <v>0.923</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15">
+        <v>0.8</v>
+      </c>
+      <c r="Q15">
+        <v>0.833</v>
+      </c>
+      <c r="R15">
+        <v>1.811</v>
+      </c>
+      <c r="S15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U15" t="s">
+        <v>28</v>
+      </c>
+      <c r="V15" t="s">
+        <v>28</v>
+      </c>
+      <c r="W15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16">
+        <v>89</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>0.865</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0.925</v>
+      </c>
+      <c r="I16">
+        <v>0.943</v>
+      </c>
+      <c r="J16">
+        <v>0.692</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N16" t="s">
+        <v>70</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>8</v>
+      </c>
+      <c r="S16" t="s">
+        <v>28</v>
+      </c>
+      <c r="T16" t="s">
+        <v>28</v>
+      </c>
+      <c r="U16" t="s">
+        <v>28</v>
+      </c>
+      <c r="V16" t="s">
+        <v>28</v>
+      </c>
+      <c r="W16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17">
+        <v>89</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>0.978</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0.989</v>
+      </c>
+      <c r="I17">
+        <v>0.989</v>
+      </c>
+      <c r="J17">
+        <v>0.923</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>72</v>
+      </c>
+      <c r="N17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17">
+        <v>0.8</v>
+      </c>
+      <c r="Q17">
+        <v>0.833</v>
+      </c>
+      <c r="R17">
+        <v>1.811</v>
+      </c>
+      <c r="S17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T17" t="s">
+        <v>28</v>
+      </c>
+      <c r="U17" t="s">
+        <v>28</v>
+      </c>
+      <c r="V17" t="s">
+        <v>28</v>
+      </c>
+      <c r="W17" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/tests/results/eval-log.xlsx
+++ b/tests/results/eval-log.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>hybrid v2: OR-ified sparse query + phrase extraction (reranked pass)</t>
+  </si>
+  <si>
+    <t>2026-08-13T13:48:02.289Z</t>
+  </si>
+  <si>
+    <t>tests\results\eval-2026-08-13T13-48-02-288Z.json</t>
   </si>
 </sst>
 </file>
@@ -613,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="23" width="20" customWidth="1"/>
@@ -1691,6 +1697,77 @@
         <v>28</v>
       </c>
     </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18">
+        <v>89</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>0.865</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0.925</v>
+      </c>
+      <c r="I18">
+        <v>0.943</v>
+      </c>
+      <c r="J18">
+        <v>0.692</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>75</v>
+      </c>
+      <c r="N18" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" t="s">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>8</v>
+      </c>
+      <c r="S18" t="s">
+        <v>28</v>
+      </c>
+      <c r="T18" t="s">
+        <v>28</v>
+      </c>
+      <c r="U18" t="s">
+        <v>28</v>
+      </c>
+      <c r="V18" t="s">
+        <v>28</v>
+      </c>
+      <c r="W18" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
